--- a/AAII_Financials/Quarterly/LULU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LULU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>LULU</t>
   </si>
@@ -656,533 +656,559 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F7" s="2">
         <v>46054</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45963</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45872</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45781</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45690</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45592</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45501</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45410</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45319</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45228</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45137</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44955</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44864</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44682</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44591</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44409</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44318</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44136</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44045</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43954</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43863</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43772</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43681</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43590</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43499</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43401</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43310</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43219</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43128</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43037</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42946</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42764</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2415600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2471600</v>
+      </c>
+      <c r="F8" s="3">
         <v>3640800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2565900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2525200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2370700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3611500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2396700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2371100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2208900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3205100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2204200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>2209200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2000800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2771800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1856900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1868300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1613500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2129100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1450400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1450600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1226500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1729500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1117400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>902900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>652000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1397500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>916100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>883400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>782300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>1167500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>747700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>723500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>649700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>928800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>619000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>581100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>520300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>789900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>544400</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1088300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1132800</v>
+      </c>
+      <c r="F9" s="3">
         <v>1642900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1140000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1048000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>987500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1429500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>995100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>958900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>933800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1301700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>947600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>910700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>850000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1244200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>818000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>812900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>743100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>892900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>621000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>607900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>526200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>716800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>490100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>413400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>317600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>586700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>411100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>397600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>360600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>498900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>340900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>327300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>305000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>406300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>297100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>283600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>263400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>362000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1327400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1338800</v>
+      </c>
+      <c r="F10" s="3">
         <v>1997900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1425900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1477200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1383100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2182000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1401600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1412200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1275100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1903400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1256700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1298500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1150800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1527600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1038900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1055400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>870400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1236200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>829400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>842700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>700300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1012700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>627300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>489500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>334400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>810800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>505000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>485800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>421700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>668600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>406800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>396200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>344700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>522500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>321900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>297500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>256900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>427900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>278400</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1224,8 +1250,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1343,8 +1371,14 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1462,13 +1496,19 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-134500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1491,71 +1531,71 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>3500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>74500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>407900</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>1500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>24100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>8100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>7700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>7800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>8500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>11500</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1564,69 +1604,75 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>2000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>21000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>3200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>12300</v>
       </c>
-      <c r="AN14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AP14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F15" s="3">
         <v>1800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>1700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>103600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>95800</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>1300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>1900</v>
-      </c>
-      <c r="P15" s="3">
-        <v>2200</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>2200</v>
       </c>
       <c r="R15" s="3">
         <v>2200</v>
@@ -1653,14 +1699,14 @@
         <v>2200</v>
       </c>
       <c r="Z15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AB15" s="3">
         <v>700</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1673,11 +1719,11 @@
       <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>0</v>
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI15" s="3">
         <v>0</v>
@@ -1700,8 +1746,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1740,246 +1792,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2096500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2194700</v>
+      </c>
+      <c r="F17" s="3">
         <v>2828500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2130000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2001400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1932000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2569300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1906000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1830900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1776200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2287700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1791600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1729900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1599400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2457400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1504500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1467100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1353100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1538600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1192500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1159600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1032600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1271600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>912500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>778500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>619200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>981000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>740300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>715400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>653500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>836000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>611800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>589300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>545400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>672500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>533400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>512300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>474900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>593300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>451400</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>319200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>276900</v>
+      </c>
+      <c r="F18" s="3">
         <v>812300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>435900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>523800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>438600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1042200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>490700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>540200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>432600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>917400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>412600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>479300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>401400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>314400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>352400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>401200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>260400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>590500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>257900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>291000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>193900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>457900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>204900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>124400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>32800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>416500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>175800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>168000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>128800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>331500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>135900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>134200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>104300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>256300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>85600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>68800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>45400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>196600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2021,246 +2087,260 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-5900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-9700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-11800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-15400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-13700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-18000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-23300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-17800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-9800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-7400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-8000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-100</v>
       </c>
       <c r="T20" s="3">
         <v>200</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V20" s="3">
+        <v>200</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>2100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>2000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>2400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>2800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>2000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>1600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>1200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>1100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>330600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>288000</v>
+      </c>
+      <c r="F21" s="3">
         <v>815100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>443500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>535300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>452000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1059100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>505500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>661800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>551700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>935200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>423700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>488500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>411300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>398300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>431900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>469300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>324800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>652900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>315900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>344800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>244500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>509300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>253400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>164700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>77500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>466100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>221800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>207400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>164000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>369700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>169600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>164500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>134000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>285600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>115200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>97900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>69500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>221500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>117600</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2300,11 +2380,11 @@
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2378,246 +2458,264 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>467400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>286100</v>
+      </c>
+      <c r="F23" s="3">
         <v>813300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>441700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>533600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>450400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1057500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>504400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>558200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>455900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>931700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>348000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>486600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>409400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>318100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>352800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>401400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>260300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>590700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>258000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>291100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>194000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>457000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>204300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>124100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>33900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>418600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>177800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>169800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>131200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>334300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>137900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>135800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>107200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>257500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>86600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>69500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>46300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>197500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>93600</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>138100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>91000</v>
+      </c>
+      <c r="F24" s="3">
         <v>226400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>134900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>162600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>135800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>309100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>152500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>165300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>134500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>262300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>99200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>145000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>119000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>198300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>97300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>111800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>70300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>156200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>70200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>83100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>49100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>127200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>60700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>37300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>5300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>120600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>51800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>44800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>34600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>113500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>38400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>40000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>32100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>78400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>27700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>20800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>15100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>61400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2735,246 +2833,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>329200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>195000</v>
+      </c>
+      <c r="F26" s="3">
         <v>586900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>306800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>370900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>314600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>748400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>351900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>392900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>321400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>669500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>248700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>341600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>290400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>119800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>255500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>289500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>190000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>434500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>187800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>208100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>145000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>329800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>143600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>86800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>28600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>298000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>126000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>125000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>96600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>220800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>99600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>95800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>75200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>179100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>58900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>48700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>31200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>136100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>68300</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>329200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>195000</v>
+      </c>
+      <c r="F27" s="3">
         <v>586900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>306800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>370900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>314600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>748400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>351900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>392900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>321400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>669500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>248700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>341600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>290400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>119800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>255500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>289500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>190000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>434500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>187800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>208100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>145000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>329800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>143600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>86800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>28600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>298000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>126000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>125000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>96600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>220800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>99600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>95800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>75200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>179100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>58900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>48700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>31200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>136100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>68300</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3092,8 +3208,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3163,45 +3285,45 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AI29" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-59300</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3211,8 +3333,14 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3330,8 +3458,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3449,246 +3583,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>5900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>9700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>11800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>15400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>13700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>18000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>23300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>17800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>9800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>7400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>8000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
       </c>
       <c r="T32" s="3">
         <v>-200</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>329200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>195000</v>
+      </c>
+      <c r="F33" s="3">
         <v>586900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>306800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>370900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>314600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>748400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>351900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>392900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>321400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>669500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>248700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>341600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>290400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>119800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>255500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>289500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>190000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>434500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>187800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>208100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>145000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>329800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>143600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>86800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>28600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>298000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>126000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>125000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>96600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>218500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>94400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>95800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>75200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>119800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>58900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>48700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>31200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>136100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>68300</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3806,251 +3958,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>329200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>195000</v>
+      </c>
+      <c r="F35" s="3">
         <v>586900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>306800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>370900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>314600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>748400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>351900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>392900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>321400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>669500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>248700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>341600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>290400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>119800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>255500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>289500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>190000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>434500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>187800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>208100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>145000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>329800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>143600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>86800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>28600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>298000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>126000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>125000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>96600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>218500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>94400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>95800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>75200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>119800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>58900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>48700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>31200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>136100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>68300</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F38" s="2">
         <v>46054</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45963</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45872</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45781</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45690</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45592</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45501</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45410</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45319</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45228</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45137</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44955</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44864</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44682</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44591</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44409</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44318</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44136</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44045</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43954</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43863</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43772</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43681</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43590</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43499</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43401</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43310</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43219</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43128</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43037</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42946</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42764</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4092,8 +4262,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4135,127 +4307,135 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1389700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1514700</v>
+      </c>
+      <c r="F41" s="3">
         <v>1807200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1035900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1155800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1325300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1984300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1188400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1610100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1900700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2244000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1091100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1107500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>950600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1154900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>352600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>498800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>649000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1259900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>993600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1170000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1179700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1150500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>481600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>523000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>823000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1093500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>586200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>623700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>576200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>881300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>703600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>777800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>966600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>990500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>650100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>721200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>698300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>734800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>480400</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4373,484 +4553,514 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>171200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>165000</v>
+      </c>
+      <c r="F43" s="3">
         <v>190700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>250300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>139300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>141200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>120200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>143400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>126100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>126300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>124800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>107000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>106200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>107500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>132900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>96200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>81800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>78400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>77000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>75300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>56200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>57000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>75700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>73100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>81600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>48700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>40200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>35700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>27700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>20100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>35800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>29400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>23500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>19200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>21300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>15900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>10700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>9200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1711500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1687100</v>
+      </c>
+      <c r="F44" s="3">
         <v>1700800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1997800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1722600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1652100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1442100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1800900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1429000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1345300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1323600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1663600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1660800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1580300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1447400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1741700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1462100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1275000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>966500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>943900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>789800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>732900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>647200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>771000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>672800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>625800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>518500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>627100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>494300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>443000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>404800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>496000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>392700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>373400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>329600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>396900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>316400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>304000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>298400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>364500</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>509100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>470600</v>
+      </c>
+      <c r="F45" s="3">
         <v>419300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>484400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>348400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>300200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>286000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>325900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>255700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>249100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>231000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>366600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>306600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>271800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>424300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>443700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>344400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>300800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>311500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>298500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>259300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>283900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>250900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>275200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>212400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>197000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>155700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>202700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>187300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>132200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>107300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>134400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>114000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>91000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>97000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>120100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>117600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>119700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>120300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>166100</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3945600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3994600</v>
+      </c>
+      <c r="F46" s="3">
         <v>4262700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3923700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3528700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3582500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3980300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3605300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3571700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3768100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4060600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3364900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3323900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3053300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3159500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2634200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2387100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2303200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2614900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2311300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2275300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2253500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2124400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1600800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1489800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1694500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1807900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1451700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1333000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1171600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1429300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>1363500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>1308000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>1452900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>1436300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>1188300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>1171000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>1132700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>1162700</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>1022900</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4890,11 +5100,11 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4968,246 +5178,264 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3993400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3994400</v>
+      </c>
+      <c r="F48" s="3">
         <v>3663900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3552400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3522400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3396000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3196900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3058300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2917800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2824900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2811400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2462500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2446400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2306300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2239000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2069200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1927800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1794800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1731300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1665900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1536000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1493800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1480500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1434000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1424300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1391100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1361400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1308900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1274100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1209700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>567200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>531300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>487500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>472300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>473600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>440400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>427000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>398800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>423500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>399700</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>188400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>189400</v>
+      </c>
+      <c r="F49" s="3">
         <v>191200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>183000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>182200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>178000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>171200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>178200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>23900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>24000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>24100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>23900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>42400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>44100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>46100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>451200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>453800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>455900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>458200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>460600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>462700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>465000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>467000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>468900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>471100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>24000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>24400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>24500</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>24200</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>24100</v>
       </c>
       <c r="AF49" s="3">
         <v>24200</v>
       </c>
       <c r="AG49" s="3">
+        <v>24100</v>
+      </c>
+      <c r="AH49" s="3">
         <v>24200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
+        <v>24200</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>24300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>24400</v>
-      </c>
-      <c r="AJ49" s="3">
-        <v>24700</v>
-      </c>
-      <c r="AK49" s="3">
-        <v>24500</v>
       </c>
       <c r="AL49" s="3">
         <v>24700</v>
       </c>
       <c r="AM49" s="3">
+        <v>24500</v>
+      </c>
+      <c r="AN49" s="3">
+        <v>24700</v>
+      </c>
+      <c r="AO49" s="3">
         <v>24200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>24600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5325,8 +5553,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5444,127 +5678,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>122100</v>
+      </c>
+      <c r="F52" s="3">
         <v>122900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>91900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>92400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>87800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>76100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>77100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>68500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>58300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>53100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>43800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>44000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>41800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>162400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>154800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>152100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>143300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>138200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>134300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>131100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>117600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>113400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>124200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>108900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>92000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>87600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>70100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>63400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>57600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>64000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>62100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>61300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>62200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>63900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>67200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>64200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>53600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>46700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5682,127 +5928,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8484600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8531400</v>
+      </c>
+      <c r="F54" s="3">
         <v>8456700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>7955200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>7523400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>7430500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>7603300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>7083700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>6744100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6828500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>7091900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>6022300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5992500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5571500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5607000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5309400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>4920700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>4697200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>4942500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>4572000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>4405100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>4329800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>4185200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3627900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3494000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3201800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>3281400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>2855100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>2694700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>2463000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>2084700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1981000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1881200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>2011700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>1998500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>1720400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>1686900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>1609300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>1657500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>1478900</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5844,8 +6102,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5887,172 +6147,180 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>346700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>294300</v>
+      </c>
+      <c r="F57" s="3">
         <v>331400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>352200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>373300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>304000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>271400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>386000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>317300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>261600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>348400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>309300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>298900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>287500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>172700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>300900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>259900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>308100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>289700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>227100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>203500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>196900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>172200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>160800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>122800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>78900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>80000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>116300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>110500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>88300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>95500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>153100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>110500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>24600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>14100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>19000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>8500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>24800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>366600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>357200</v>
+      </c>
+      <c r="F58" s="3">
         <v>298700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>317500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>297900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>281800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>275200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>290400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>278100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>254400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>249300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>217100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>216800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>210500</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6098,18 +6366,18 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
+      <c r="AG58" s="3">
+        <v>0</v>
       </c>
       <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>100000</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
@@ -6125,291 +6393,309 @@
       <c r="AO58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>628500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>627400</v>
+      </c>
+      <c r="F59" s="3">
         <v>651400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>528500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>425000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>492000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>742900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>534700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>410400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>473600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>477600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>378400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>369400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>376300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1319500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1022000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>947300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>898800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1115600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>891000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>777800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>767900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>710900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>570100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>640500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>552600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>540400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>458500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>442100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>414700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>404900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>290500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>238600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>251100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>268000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>226500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>205200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>197400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>216600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>203600</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1801700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1794300</v>
+      </c>
+      <c r="F60" s="3">
         <v>1887500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1842200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1557300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1572400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1839600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1803500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1468700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1383600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1631300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1448100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1386400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1256800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1492200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1322800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1207200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1206900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1405300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1118000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>981400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>964800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>883200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>730900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>763300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>631500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>620400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>574800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>552600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>502900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>500500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>443700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>449200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>267300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>292600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>240600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>224300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>206000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>241400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>212700</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1774500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1778800</v>
+      </c>
+      <c r="F61" s="3">
         <v>1499700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1445300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1464800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1424900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1300600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1223700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1180800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1147600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1154000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>951000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>976700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>888600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -6482,127 +6768,139 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>57500</v>
+      </c>
+      <c r="F62" s="3">
         <v>55400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>54100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>51600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>45500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>40800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>37400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>34100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>48300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>45100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>43500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>40600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>51600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>966000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>947400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>855700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>822300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>797100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>795500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>752600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>725200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>743500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>734100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>729600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>734500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>708700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>631600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>634800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>593400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>138300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>130600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>111800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>108100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>108900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>58600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>64800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>55700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>56100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>61800</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6720,8 +7018,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6839,8 +7143,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6958,127 +7268,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3693400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3705800</v>
+      </c>
+      <c r="F66" s="3">
         <v>3494900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3453200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3136200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3141000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3279200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3097900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2712500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2608700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2859900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2496400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2459000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2251500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2458200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2270200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2062900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2029200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2202400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1913600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1733900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1690000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1626600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1465000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1492900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1366000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1329100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1206400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1187400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1096300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>638700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>574300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>560900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>375500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>401500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>299200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>289100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>261600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>297600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7120,8 +7442,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7239,8 +7563,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7358,8 +7688,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7477,8 +7813,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7596,127 +7938,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4364000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4361300</v>
+      </c>
+      <c r="F72" s="3">
         <v>4522600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4204000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4085600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3993200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4109700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3694500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3751700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3944000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3920400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3304700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3267600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3118600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2926100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2875000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>2636400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2471400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2512800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2398200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2445800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2408000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2346400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>2016600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1872900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1786100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1820600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1522900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1404900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1281400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1346900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>1310500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>1224000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>1530100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>1455000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>1336200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>1285600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>1313000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>1294200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>1158800</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7834,8 +8188,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7953,8 +8313,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8072,127 +8438,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4791200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4825600</v>
+      </c>
+      <c r="F76" s="3">
         <v>4961800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4502000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4387300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4289600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4324000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3985700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4031600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4219800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4232100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3525800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3533500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3320100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3148800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3039200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>2857800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2668100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2740000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2658500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>2671200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2639900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2558600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>2163000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>2001100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1835800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1952200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1648700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1507400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1366700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1446000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>1406800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>1320200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>1636200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>1597000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>1421300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>1397800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>1347700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>1360000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>1204500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8310,251 +8688,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F80" s="2">
         <v>46054</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45963</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45872</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45781</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45690</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45592</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45501</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45410</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45319</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45228</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45137</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44955</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44864</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44682</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44591</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44409</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44318</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44136</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44045</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43954</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43863</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43772</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43681</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43590</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43499</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43401</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43310</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43219</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43128</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43037</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42946</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42764</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>329200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>195000</v>
+      </c>
+      <c r="F81" s="3">
         <v>586900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>306800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>370900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>314600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>748400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>351900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>392900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>321400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>669500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>248700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>341600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>290400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>119800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>255500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>289500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>190000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>434500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>187800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>208100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>145000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>329800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>143600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>86800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>28600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>298000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>126000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>125000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>96600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>218500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>94400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>95800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>75200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>119800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>58900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>48700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>31200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>136100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>68300</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8596,127 +8992,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>112900</v>
+      </c>
+      <c r="F83" s="3">
         <v>132000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>112500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>103600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>95800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>103300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>96700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>92100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>82200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>78000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>77000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>65800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>62300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>80200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>79200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>68000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>64500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>62100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>58000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>53600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>50500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>52300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>49000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>40600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>43500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>47500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>44000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>37600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>32800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>35400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>31700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>28700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>26800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>28100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>28600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>28400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>23200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>24100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8834,8 +9238,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8953,8 +9363,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9072,8 +9488,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9191,8 +9613,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9310,127 +9738,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>374800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>214400</v>
+      </c>
+      <c r="F89" s="3">
         <v>1142900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>249900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>328700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-119000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1401400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>300700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>443100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>127500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1384100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>389900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>476700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>45500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1046300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>65800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>97600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-243300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>731000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>158400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>285700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>214100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>717900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>25300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>181300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-121200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>574200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>45100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>112800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-62800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>425900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>106900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>174200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>35800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>358000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>29300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>82600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>19400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>287700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9472,127 +9912,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-149700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-127400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-183200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-167400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-177900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-152300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-235000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-178500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-145100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-130700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-206500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-162900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-145500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-136900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-207000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-175600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-144700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-111400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-127500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-122500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-80300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-64200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-58400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-66100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-52600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-52100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-68800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-78500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-67300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-68400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-69100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-72700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-49700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-34300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-50700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-57200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-19900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-86700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-69800</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9710,8 +10158,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9829,127 +10283,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-143000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-138900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-173100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-169100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-213100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-106800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-223000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-308600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-135100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-131500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-208800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-161700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-145400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-138200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-183100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-161900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-123600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-101300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-114500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-111900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-116000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-85500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-79000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-71200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-499700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-45600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-65900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-80500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-68100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-63900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-76900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-76600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-34300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-53300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-70200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-30000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-19900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-43300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-34900</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9991,8 +10457,10 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10032,11 +10500,11 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10110,8 +10578,14 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10229,8 +10703,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10348,8 +10828,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10467,361 +10953,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-333700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-378500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-269700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-194200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-276800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-468000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-324000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-412000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-587900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-328600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-38200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-204900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-190300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-115400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-68100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-14900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-125000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-259600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-321800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-232400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-168500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-122200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>8400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-90600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>2400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-170300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-183900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-106100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-302100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>2800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-8800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-77400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-14500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>34700</v>
+      </c>
+      <c r="F101" s="3">
         <v>-58500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-10700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-10700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>15800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-39600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>15900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>3900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>7100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-35300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-6700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>7100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-35300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-6700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-28500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>9600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-10800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>22800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>29400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>3700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>10000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>6400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>3400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-8100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>12500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>1700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-27400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>32900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-21500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>47700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-21600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>11400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AQ101" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-125000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-292500</v>
+      </c>
+      <c r="F102" s="3">
         <v>771300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-119900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-169500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-659100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>795900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-421700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-290600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-343300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1152800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-16400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>156900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-204300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>802200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-146200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-150200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-610900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>266300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-176500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-9700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>29200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>668900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-41400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-300000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-270500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>507400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-37600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>47500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-305100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>177700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-74200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-188700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-23900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>340400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-71200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>22900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-36600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>254500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>-55000</v>
       </c>
     </row>
